--- a/Tubex_Aug26.xlsx
+++ b/Tubex_Aug26.xlsx
@@ -3927,7 +3927,7 @@
       <c r="G3" s="258"/>
       <c r="H3" s="263">
         <f ca="1">TODAY()-1</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="I3" s="256"/>
       <c r="J3" s="256"/>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="C5" s="220">
         <f ca="1">TODAY()-1</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D5" s="114" t="s">
         <v>3</v>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="C7" s="221">
         <f ca="1">TODAY()-1</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D7" s="121" t="s">
         <v>11</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="H1" s="136">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="I1" s="10"/>
       <c r="J1" s="11"/>
@@ -50901,7 +50901,7 @@
       </c>
       <c r="J1" s="63">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="64" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -51213,7 +51213,7 @@
       <c r="I12" s="67"/>
       <c r="J12" s="63">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">

--- a/Tubex_Aug26.xlsx
+++ b/Tubex_Aug26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_4897355300C1F4140458C7950DBC70C25139750A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_C998E32FB79E15047C00875905D4C0BA5B737219" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4133" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4158" uniqueCount="618">
   <si>
     <t>AUGUST 2026 Tube Required Orders</t>
   </si>
@@ -1821,7 +1821,7 @@
     <t>Top 10 inks = 81.7% of all consumption. Remaining 15 inks share 18.3%.  Source: ERP ST_Stk_Cons_YFI.rpt · May 2025–Apr 2026 · 8,617,293 pcs produced.</t>
   </si>
   <si>
-    <t>FG STOCK IN HAND — Last Updated: 08-Aug-2026</t>
+    <t>FG STOCK IN HAND — Last Updated: 10-Aug-2026</t>
   </si>
   <si>
     <t>Shows latest date only from FG Stock In hand (Production.xlsx). Older dates are discarded. Re-run update_production.py to refresh.</t>
@@ -3970,8 +3970,8 @@
     <col min="13" max="13" width="14.7109375" style="105" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="105" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="105" customWidth="1"/>
-    <col min="16" max="134" width="8.7109375" style="105" customWidth="1"/>
-    <col min="135" max="16384" width="8.7109375" style="105"/>
+    <col min="16" max="135" width="8.7109375" style="105" customWidth="1"/>
+    <col min="136" max="16384" width="8.7109375" style="105"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -4049,7 +4049,7 @@
       <c r="G3" s="264"/>
       <c r="H3" s="266">
         <f ca="1">TODAY()-1</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="I3" s="262"/>
       <c r="J3" s="262"/>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="C5" s="195">
         <f ca="1">TODAY()-1</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="D5" s="107" t="s">
         <v>149</v>
@@ -4151,18 +4151,18 @@
       <c r="A6" s="102"/>
       <c r="B6" s="265">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8963=MAX(Production_Log!$A$3:$A$8963))*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v>19516</v>
+        <v>23128</v>
       </c>
       <c r="C6" s="262"/>
       <c r="D6" s="111">
         <f>SUMIF($B$11:$B$66,"TUBE",$H$11:$H$66)</f>
-        <v>112560</v>
+        <v>135688</v>
       </c>
       <c r="E6" s="265"/>
       <c r="F6" s="262"/>
       <c r="G6" s="112">
         <f t="array" ref="G6">IFERROR(SUMPRODUCT((Production_Log!$F$3:$F$8963&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$I$3:$I$8963)/SUMPRODUCT((Production_Log!$F$3:$F$8963&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*(Production_Log!$H$3:$H$8963+Production_Log!$I$3:$I$8963)),"-")</f>
-        <v>2.0961990084369837E-2</v>
+        <v>2.1066605102158607E-2</v>
       </c>
       <c r="H6" s="112"/>
       <c r="I6" s="109"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C7" s="196">
         <f ca="1">TODAY()-1</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="D7" s="114" t="s">
         <v>156</v>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="O7" s="125">
         <f t="shared" ref="O7:O13" si="0">IFERROR(N7/$N$14,"")</f>
-        <v>0.74193548387096775</v>
+        <v>0.65714285714285714</v>
       </c>
       <c r="P7" s="102"/>
       <c r="Q7" s="102"/>
@@ -4251,7 +4251,7 @@
       <c r="A8" s="102"/>
       <c r="B8" s="270">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8963=MAX(Production_Log!$A$3:$A$8963))*(Production_Log!$B$3:$B$8963="PF Machine")*Production_Log!$H$3:$H$8963)</f>
-        <v>5520</v>
+        <v>0</v>
       </c>
       <c r="C8" s="262"/>
       <c r="D8" s="117">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="O8" s="125">
         <f t="shared" si="0"/>
-        <v>0.25806451612903225</v>
+        <v>0.22857142857142856</v>
       </c>
       <c r="P8" s="102"/>
       <c r="Q8" s="102"/>
@@ -4316,15 +4316,15 @@
       <c r="L9" s="272"/>
       <c r="M9" s="123" t="str">
         <f>IFERROR(INDEX($S$9:$S$22,MATCH(LARGE($U$9:$U$22,3),$U$9:$U$22,0)),"")</f>
-        <v>Workers Shortage</v>
+        <v>Mechanical</v>
       </c>
       <c r="N9" s="124">
         <f>IFERROR(INDEX($T$9:$T$22,MATCH(LARGE($U$9:$U$22,3),$U$9:$U$22,0)),"")/60</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O9" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.11428571428571428</v>
       </c>
       <c r="P9" s="102"/>
       <c r="Q9" s="102"/>
@@ -4334,11 +4334,11 @@
       </c>
       <c r="T9" s="131">
         <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$8963,5)="Press")+(LEFT(Production_Log!$B$3:$B$8963,5)="Print"))*Production_Log!$K$3:$K$8963)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U9" s="130">
         <f>T9+0.00001</f>
-        <v>1.0000000000000001E-5</v>
+        <v>120.00001</v>
       </c>
       <c r="V9" s="104"/>
       <c r="W9" s="104"/>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="M10" s="123" t="str">
         <f>IFERROR(INDEX($S$9:$S$22,MATCH(LARGE($U$9:$U$22,4),$U$9:$U$22,0)),"")</f>
-        <v>Power Shutdown</v>
+        <v>Workers Shortage</v>
       </c>
       <c r="N10" s="124">
         <f>IFERROR(INDEX($T$9:$T$22,MATCH(LARGE($U$9:$U$22,4),$U$9:$U$22,0)),"")/60</f>
@@ -4441,11 +4441,11 @@
       </c>
       <c r="H11" s="253">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F11)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v>38304</v>
+        <v>43344</v>
       </c>
       <c r="I11" s="252">
         <f>G11-H11</f>
-        <v>-38304</v>
+        <v>-43344</v>
       </c>
       <c r="J11" s="254" t="str">
         <f>IF(G11=0,"-",H11/G11)</f>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="M11" s="123" t="str">
         <f>IFERROR(INDEX($S$9:$S$22,MATCH(LARGE($U$9:$U$22,5),$U$9:$U$22,0)),"")</f>
-        <v>Changeover</v>
+        <v>Power Shutdown</v>
       </c>
       <c r="N11" s="124">
         <f>IFERROR(INDEX($T$9:$T$22,MATCH(LARGE($U$9:$U$22,5),$U$9:$U$22,0)),"")/60</f>
@@ -4499,19 +4499,19 @@
       </c>
       <c r="G12" s="252">
         <f>IFERROR(INDEX(MRP!$F$3:$F$3,MATCH(Tubex_Dashboard!F12,MRP!$D$3:$D$3,0)),0)</f>
-        <v>306188</v>
+        <v>259778</v>
       </c>
       <c r="H12" s="253">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F12)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v>74256</v>
+        <v>92344</v>
       </c>
       <c r="I12" s="252">
         <f>G12-H12</f>
-        <v>231932</v>
+        <v>167434</v>
       </c>
       <c r="J12" s="254">
         <f>IF(G12=0,"-",H12/G12)</f>
-        <v>0.24251766888316981</v>
+        <v>0.3554727498094527</v>
       </c>
       <c r="K12" s="253">
         <v>68068</v>
@@ -4519,7 +4519,7 @@
       <c r="L12" s="255"/>
       <c r="M12" s="123" t="str">
         <f>IFERROR(INDEX($S$9:$S$22,MATCH(LARGE($U$9:$U$22,6),$U$9:$U$22,0)),"")</f>
-        <v>Electrical</v>
+        <v>Changeover</v>
       </c>
       <c r="N12" s="124">
         <f>IFERROR(INDEX($T$9:$T$22,MATCH(LARGE($U$9:$U$22,6),$U$9:$U$22,0)),"")/60</f>
@@ -4563,15 +4563,15 @@
       <c r="F13" s="257"/>
       <c r="G13" s="259">
         <f>SUM(G11:G12)</f>
-        <v>306188</v>
+        <v>259778</v>
       </c>
       <c r="H13" s="259">
         <f>SUM(H11:H12)</f>
-        <v>112560</v>
+        <v>135688</v>
       </c>
       <c r="I13" s="259">
         <f>SUMIF(I11:I12,"&gt;"&amp;0)</f>
-        <v>231932</v>
+        <v>167434</v>
       </c>
       <c r="J13" s="259"/>
       <c r="K13" s="259">
@@ -4581,7 +4581,7 @@
       <c r="L13" s="259"/>
       <c r="M13" s="123" t="str">
         <f>IFERROR(INDEX($S$9:$S$22,MATCH(LARGE($U$9:$U$22,7),$U$9:$U$22,0)),"")</f>
-        <v>Mechanical</v>
+        <v>Electrical</v>
       </c>
       <c r="N13" s="124">
         <f>IFERROR(INDEX($T$9:$T$22,MATCH(LARGE($U$9:$U$22,7),$U$9:$U$22,0)),"")/60</f>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="N14" s="121">
         <f>SUM($T$9:$T$22)/60</f>
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="O14" s="121" t="s">
         <v>173</v>
@@ -9054,7 +9054,7 @@
     <col min="7" max="7" width="11.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="17.5703125" style="4" customWidth="1"/>
     <col min="9" max="9" width="15" style="3" customWidth="1"/>
-    <col min="10" max="10" width="45.5703125" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="H1" s="129">
         <f ca="1">TODAY()</f>
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="I1" s="10"/>
       <c r="J1" s="11"/>
@@ -9144,16 +9144,15 @@
         <v>6900</v>
       </c>
       <c r="F3" s="204">
-        <f>G3+231932</f>
-        <v>306188</v>
+        <v>259778</v>
       </c>
       <c r="G3" s="204">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D3,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>74256</v>
+        <v>92344</v>
       </c>
       <c r="H3" s="205">
         <f>F3-G3</f>
-        <v>231932</v>
+        <v>167434</v>
       </c>
       <c r="I3" s="205"/>
     </row>
@@ -9167,15 +9166,15 @@
       </c>
       <c r="F4" s="122">
         <f>SUM(F3:F3)</f>
-        <v>306188</v>
+        <v>259778</v>
       </c>
       <c r="G4" s="122">
         <f>SUM(G3:G3)</f>
-        <v>74256</v>
+        <v>92344</v>
       </c>
       <c r="H4" s="122">
         <f>SUMIF(H3:H3, "&gt;0")</f>
-        <v>231932</v>
+        <v>167434</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="11"/>
@@ -9568,11 +9567,11 @@
       </c>
       <c r="F14" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A14,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A14,TableInventory[Item ID],0)),0)</f>
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="G14" s="199">
         <f t="shared" si="0"/>
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="H14" s="226" t="str">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A14)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F14/(SUMPRODUCT((TableBOM[Item ID]=A14)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -9678,19 +9677,19 @@
       </c>
       <c r="E17" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A17)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>2041.0016000000001</v>
+        <v>1473.4192000000003</v>
       </c>
       <c r="F17" s="200">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A17,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A17,TableInventory[Item ID],0)),0)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G17" s="199">
         <f t="shared" si="0"/>
-        <v>-1991.0016000000001</v>
+        <v>-1473.4192000000003</v>
       </c>
       <c r="H17" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A17)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F17/(SUMPRODUCT((TableBOM[Item ID]=A17)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>6250</v>
+        <v>0</v>
       </c>
       <c r="I17" s="201" t="str">
         <f t="shared" si="1"/>
@@ -10037,7 +10036,7 @@
       </c>
       <c r="E25" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A25)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>71.435056000000017</v>
+        <v>51.569672000000004</v>
       </c>
       <c r="F25" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A25,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A25,TableInventory[Item ID],0)),0)</f>
@@ -10045,7 +10044,7 @@
       </c>
       <c r="G25" s="199">
         <f t="shared" si="0"/>
-        <v>3.5649439999999828</v>
+        <v>23.430327999999996</v>
       </c>
       <c r="H25" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A25)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F25/(SUMPRODUCT((TableBOM[Item ID]=A25)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -10053,7 +10052,7 @@
       </c>
       <c r="I25" s="201" t="str">
         <f t="shared" si="2"/>
-        <v>LOW</v>
+        <v>OK</v>
       </c>
       <c r="J25" s="228" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A25)&gt;0)*($H$3&gt;0),$C$3&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A25)&gt;0)*($H$3&gt;0),$C$3&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A25)&gt;0)*($H$3&gt;0),$C$3&amp;", ",""))-2),"")</f>
@@ -10221,7 +10220,7 @@
       </c>
       <c r="E29" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A29)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>170.93388400000001</v>
+        <v>123.39885800000002</v>
       </c>
       <c r="F29" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A29,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A29,TableInventory[Item ID],0)),0)</f>
@@ -10229,7 +10228,7 @@
       </c>
       <c r="G29" s="199">
         <f t="shared" si="0"/>
-        <v>-140.93388400000001</v>
+        <v>-93.398858000000018</v>
       </c>
       <c r="H29" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A29)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F29/(SUMPRODUCT((TableBOM[Item ID]=A29)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -10549,7 +10548,7 @@
       </c>
       <c r="E37" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A37)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>71.435056000000017</v>
+        <v>51.569672000000004</v>
       </c>
       <c r="F37" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A37,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A37,TableInventory[Item ID],0)),0)</f>
@@ -10557,7 +10556,7 @@
       </c>
       <c r="G37" s="199">
         <f t="shared" si="0"/>
-        <v>-26.435056000000017</v>
+        <v>-6.5696720000000042</v>
       </c>
       <c r="H37" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A37)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F37/(SUMPRODUCT((TableBOM[Item ID]=A37)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -11142,7 +11141,7 @@
       </c>
       <c r="E52" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A52)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>236570.64</v>
+        <v>170782.68</v>
       </c>
       <c r="F52" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A52,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A52,TableInventory[Item ID],0)),0)</f>
@@ -11150,7 +11149,7 @@
       </c>
       <c r="G52" s="199">
         <f t="shared" si="3"/>
-        <v>-136570.64000000001</v>
+        <v>-70782.679999999993</v>
       </c>
       <c r="H52" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A52)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F52/(SUMPRODUCT((TableBOM[Item ID]=A52)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -11634,7 +11633,7 @@
       </c>
       <c r="E65" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A65)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>1071.9340403199999</v>
+        <v>773.83976384000005</v>
       </c>
       <c r="F65" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A65,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A65,TableInventory[Item ID],0)),0)</f>
@@ -11642,7 +11641,7 @@
       </c>
       <c r="G65" s="199">
         <f t="shared" si="3"/>
-        <v>-878.93404031999989</v>
+        <v>-580.83976384000005</v>
       </c>
       <c r="H65" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A65)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F65/(SUMPRODUCT((TableBOM[Item ID]=A65)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -11786,7 +11785,7 @@
       </c>
       <c r="E69" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A69)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>2.1226416640000001</v>
+        <v>1.5323559680000001</v>
       </c>
       <c r="F69" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A69,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A69,TableInventory[Item ID],0)),0)</f>
@@ -11794,7 +11793,7 @@
       </c>
       <c r="G69" s="199">
         <f t="shared" si="3"/>
-        <v>37.877358336</v>
+        <v>38.467644032000003</v>
       </c>
       <c r="H69" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A69)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F69/(SUMPRODUCT((TableBOM[Item ID]=A69)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -11870,7 +11869,7 @@
       </c>
       <c r="E71" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A71)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>39.799531199999997</v>
+        <v>28.731674399999999</v>
       </c>
       <c r="F71" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A71,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A71,TableInventory[Item ID],0)),0)</f>
@@ -11878,7 +11877,7 @@
       </c>
       <c r="G71" s="199">
         <f t="shared" ref="G71:G102" si="6">F71-E71</f>
-        <v>393.20046880000001</v>
+        <v>404.26832560000003</v>
       </c>
       <c r="H71" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A71)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F71/(SUMPRODUCT((TableBOM[Item ID]=A71)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -13242,7 +13241,7 @@
         <v>410</v>
       </c>
       <c r="J3" s="234">
-        <f t="shared" ref="J3:J40" si="0">IFERROR(I3/(H3+I3),"")</f>
+        <f t="shared" ref="J3:J48" si="0">IFERROR(I3/(H3+I3),"")</f>
         <v>1.6400000000000001E-2</v>
       </c>
       <c r="K3" s="232"/>
@@ -14846,172 +14845,344 @@
       <c r="S40" s="232"/>
     </row>
     <row r="41" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="176"/>
-      <c r="B41" s="177"/>
-      <c r="C41" s="177"/>
-      <c r="D41" s="177"/>
-      <c r="E41" s="177"/>
-      <c r="F41" s="177"/>
-      <c r="G41" s="178"/>
-      <c r="H41" s="178"/>
-      <c r="I41" s="178"/>
-      <c r="J41" s="179"/>
-      <c r="K41" s="177"/>
-      <c r="L41" s="177"/>
-      <c r="M41" s="177"/>
-      <c r="N41" s="177"/>
-      <c r="O41" s="177"/>
-      <c r="P41" s="177"/>
-      <c r="Q41" s="177"/>
-      <c r="R41" s="177"/>
-      <c r="S41" s="177"/>
+      <c r="A41" s="231">
+        <v>46242</v>
+      </c>
+      <c r="B41" s="232" t="s">
+        <v>256</v>
+      </c>
+      <c r="C41" s="232" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="232" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="232">
+        <v>30</v>
+      </c>
+      <c r="F41" s="232">
+        <v>6206</v>
+      </c>
+      <c r="G41" s="233">
+        <v>14000</v>
+      </c>
+      <c r="H41" s="233">
+        <v>13750</v>
+      </c>
+      <c r="I41" s="233">
+        <v>250</v>
+      </c>
+      <c r="J41" s="234">
+        <f t="shared" si="0"/>
+        <v>1.7857142857142856E-2</v>
+      </c>
+      <c r="K41" s="232"/>
+      <c r="L41" s="232"/>
+      <c r="M41" s="232"/>
+      <c r="N41" s="232"/>
+      <c r="O41" s="232"/>
+      <c r="P41" s="232"/>
+      <c r="Q41" s="232"/>
+      <c r="R41" s="232"/>
+      <c r="S41" s="232"/>
     </row>
     <row r="42" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="176"/>
-      <c r="B42" s="177"/>
-      <c r="C42" s="177"/>
-      <c r="D42" s="177"/>
-      <c r="E42" s="177"/>
-      <c r="F42" s="177"/>
-      <c r="G42" s="178"/>
-      <c r="H42" s="178"/>
-      <c r="I42" s="178"/>
-      <c r="J42" s="179"/>
-      <c r="K42" s="177"/>
-      <c r="L42" s="177"/>
-      <c r="M42" s="177"/>
-      <c r="N42" s="177"/>
-      <c r="O42" s="177"/>
-      <c r="P42" s="177"/>
-      <c r="Q42" s="177"/>
-      <c r="R42" s="177"/>
-      <c r="S42" s="177"/>
+      <c r="A42" s="231">
+        <v>46242</v>
+      </c>
+      <c r="B42" s="232" t="s">
+        <v>261</v>
+      </c>
+      <c r="C42" s="232" t="s">
+        <v>127</v>
+      </c>
+      <c r="D42" s="232" t="s">
+        <v>168</v>
+      </c>
+      <c r="E42" s="232">
+        <v>25</v>
+      </c>
+      <c r="F42" s="232">
+        <v>5389</v>
+      </c>
+      <c r="G42" s="233">
+        <v>8000</v>
+      </c>
+      <c r="H42" s="233">
+        <v>7880</v>
+      </c>
+      <c r="I42" s="233">
+        <v>120</v>
+      </c>
+      <c r="J42" s="234">
+        <f t="shared" si="0"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K42" s="232"/>
+      <c r="L42" s="232"/>
+      <c r="M42" s="232"/>
+      <c r="N42" s="232"/>
+      <c r="O42" s="232"/>
+      <c r="P42" s="232"/>
+      <c r="Q42" s="232"/>
+      <c r="R42" s="232"/>
+      <c r="S42" s="232"/>
     </row>
     <row r="43" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="176"/>
-      <c r="B43" s="177"/>
-      <c r="C43" s="177"/>
-      <c r="D43" s="177"/>
-      <c r="E43" s="177"/>
-      <c r="F43" s="177"/>
-      <c r="G43" s="178"/>
-      <c r="H43" s="178"/>
-      <c r="I43" s="178"/>
-      <c r="J43" s="179"/>
-      <c r="K43" s="177"/>
-      <c r="L43" s="177"/>
-      <c r="M43" s="177"/>
-      <c r="N43" s="177"/>
-      <c r="O43" s="177"/>
-      <c r="P43" s="177"/>
-      <c r="Q43" s="177"/>
-      <c r="R43" s="177"/>
-      <c r="S43" s="177"/>
+      <c r="A43" s="231">
+        <v>46242</v>
+      </c>
+      <c r="B43" s="232" t="s">
+        <v>257</v>
+      </c>
+      <c r="C43" s="232" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="232" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="232">
+        <v>30</v>
+      </c>
+      <c r="F43" s="232">
+        <v>6206</v>
+      </c>
+      <c r="G43" s="233">
+        <v>24276</v>
+      </c>
+      <c r="H43" s="233">
+        <v>24256</v>
+      </c>
+      <c r="I43" s="233">
+        <v>20</v>
+      </c>
+      <c r="J43" s="234">
+        <f t="shared" si="0"/>
+        <v>8.2385895534684461E-4</v>
+      </c>
+      <c r="K43" s="232"/>
+      <c r="L43" s="232"/>
+      <c r="M43" s="232"/>
+      <c r="N43" s="232"/>
+      <c r="O43" s="232"/>
+      <c r="P43" s="232"/>
+      <c r="Q43" s="232"/>
+      <c r="R43" s="232"/>
+      <c r="S43" s="232"/>
     </row>
     <row r="44" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="176"/>
-      <c r="B44" s="177"/>
-      <c r="C44" s="177"/>
-      <c r="D44" s="177"/>
-      <c r="E44" s="177"/>
-      <c r="F44" s="177"/>
-      <c r="G44" s="178"/>
-      <c r="H44" s="178"/>
-      <c r="I44" s="178"/>
-      <c r="J44" s="179"/>
-      <c r="K44" s="177"/>
-      <c r="L44" s="177"/>
-      <c r="M44" s="177"/>
-      <c r="N44" s="177"/>
-      <c r="O44" s="177"/>
-      <c r="P44" s="177"/>
-      <c r="Q44" s="177"/>
-      <c r="R44" s="177"/>
-      <c r="S44" s="177"/>
+      <c r="A44" s="231">
+        <v>46242</v>
+      </c>
+      <c r="B44" s="232" t="s">
+        <v>258</v>
+      </c>
+      <c r="C44" s="232" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" s="232" t="s">
+        <v>175</v>
+      </c>
+      <c r="E44" s="232" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44" s="232">
+        <v>8001</v>
+      </c>
+      <c r="G44" s="233">
+        <v>0</v>
+      </c>
+      <c r="H44" s="233">
+        <v>0</v>
+      </c>
+      <c r="I44" s="233">
+        <v>0</v>
+      </c>
+      <c r="J44" s="234" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K44" s="232">
+        <v>960</v>
+      </c>
+      <c r="L44" s="232"/>
+      <c r="M44" s="232"/>
+      <c r="N44" s="232"/>
+      <c r="O44" s="232"/>
+      <c r="P44" s="232"/>
+      <c r="Q44" s="232"/>
+      <c r="R44" s="232"/>
+      <c r="S44" s="232"/>
     </row>
     <row r="45" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="176"/>
-      <c r="B45" s="177"/>
-      <c r="C45" s="177"/>
-      <c r="D45" s="177"/>
-      <c r="E45" s="177"/>
-      <c r="F45" s="177"/>
-      <c r="G45" s="178"/>
-      <c r="H45" s="178"/>
-      <c r="I45" s="178"/>
-      <c r="J45" s="179"/>
-      <c r="K45" s="177"/>
-      <c r="L45" s="177"/>
-      <c r="M45" s="177"/>
-      <c r="N45" s="177"/>
-      <c r="O45" s="177"/>
-      <c r="P45" s="177"/>
-      <c r="Q45" s="177"/>
-      <c r="R45" s="177"/>
-      <c r="S45" s="177"/>
+      <c r="A45" s="231">
+        <v>46242</v>
+      </c>
+      <c r="B45" s="232" t="s">
+        <v>259</v>
+      </c>
+      <c r="C45" s="232" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="232" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="232">
+        <v>30</v>
+      </c>
+      <c r="F45" s="232">
+        <v>6206</v>
+      </c>
+      <c r="G45" s="233">
+        <v>6800</v>
+      </c>
+      <c r="H45" s="233">
+        <v>6720</v>
+      </c>
+      <c r="I45" s="233">
+        <v>80</v>
+      </c>
+      <c r="J45" s="234">
+        <f t="shared" si="0"/>
+        <v>1.1764705882352941E-2</v>
+      </c>
+      <c r="K45" s="232"/>
+      <c r="L45" s="232"/>
+      <c r="M45" s="232"/>
+      <c r="N45" s="232"/>
+      <c r="O45" s="232"/>
+      <c r="P45" s="232"/>
+      <c r="Q45" s="232"/>
+      <c r="R45" s="232"/>
+      <c r="S45" s="232"/>
     </row>
     <row r="46" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="176"/>
-      <c r="B46" s="177"/>
-      <c r="C46" s="177"/>
-      <c r="D46" s="177"/>
-      <c r="E46" s="177"/>
-      <c r="F46" s="177"/>
-      <c r="G46" s="178"/>
-      <c r="H46" s="178"/>
-      <c r="I46" s="178"/>
-      <c r="J46" s="179"/>
-      <c r="K46" s="177"/>
-      <c r="L46" s="177"/>
-      <c r="M46" s="177"/>
-      <c r="N46" s="177"/>
-      <c r="O46" s="177"/>
-      <c r="P46" s="177"/>
-      <c r="Q46" s="177"/>
-      <c r="R46" s="177"/>
-      <c r="S46" s="177"/>
+      <c r="A46" s="231">
+        <v>46242</v>
+      </c>
+      <c r="B46" s="232" t="s">
+        <v>262</v>
+      </c>
+      <c r="C46" s="232" t="s">
+        <v>127</v>
+      </c>
+      <c r="D46" s="232" t="s">
+        <v>168</v>
+      </c>
+      <c r="E46" s="232">
+        <v>25</v>
+      </c>
+      <c r="F46" s="232">
+        <v>5389</v>
+      </c>
+      <c r="G46" s="233">
+        <v>9200</v>
+      </c>
+      <c r="H46" s="233">
+        <v>9105</v>
+      </c>
+      <c r="I46" s="233">
+        <v>95</v>
+      </c>
+      <c r="J46" s="234">
+        <f t="shared" si="0"/>
+        <v>1.0326086956521738E-2</v>
+      </c>
+      <c r="K46" s="232">
+        <v>120</v>
+      </c>
+      <c r="L46" s="232"/>
+      <c r="M46" s="232"/>
+      <c r="N46" s="232"/>
+      <c r="O46" s="232"/>
+      <c r="P46" s="232"/>
+      <c r="Q46" s="232"/>
+      <c r="R46" s="232"/>
+      <c r="S46" s="232"/>
     </row>
     <row r="47" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="176"/>
-      <c r="B47" s="177"/>
-      <c r="C47" s="177"/>
-      <c r="D47" s="177"/>
-      <c r="E47" s="177"/>
-      <c r="F47" s="177"/>
-      <c r="G47" s="178"/>
-      <c r="H47" s="178"/>
-      <c r="I47" s="178"/>
-      <c r="J47" s="179"/>
-      <c r="K47" s="177"/>
-      <c r="L47" s="177"/>
-      <c r="M47" s="177"/>
-      <c r="N47" s="177"/>
-      <c r="O47" s="177"/>
-      <c r="P47" s="177"/>
-      <c r="Q47" s="177"/>
-      <c r="R47" s="177"/>
-      <c r="S47" s="177"/>
+      <c r="A47" s="231">
+        <v>46242</v>
+      </c>
+      <c r="B47" s="232" t="s">
+        <v>263</v>
+      </c>
+      <c r="C47" s="232" t="s">
+        <v>127</v>
+      </c>
+      <c r="D47" s="232" t="s">
+        <v>168</v>
+      </c>
+      <c r="E47" s="232">
+        <v>25</v>
+      </c>
+      <c r="F47" s="232">
+        <v>5389</v>
+      </c>
+      <c r="G47" s="233">
+        <v>5200</v>
+      </c>
+      <c r="H47" s="233">
+        <v>5040</v>
+      </c>
+      <c r="I47" s="233">
+        <v>160</v>
+      </c>
+      <c r="J47" s="234">
+        <f t="shared" si="0"/>
+        <v>3.0769230769230771E-2</v>
+      </c>
+      <c r="K47" s="232"/>
+      <c r="L47" s="232"/>
+      <c r="M47" s="232"/>
+      <c r="N47" s="232"/>
+      <c r="O47" s="232"/>
+      <c r="P47" s="232"/>
+      <c r="Q47" s="232"/>
+      <c r="R47" s="232"/>
+      <c r="S47" s="232"/>
     </row>
     <row r="48" spans="1:19" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="176"/>
-      <c r="B48" s="177"/>
-      <c r="C48" s="177"/>
-      <c r="D48" s="177"/>
-      <c r="E48" s="177"/>
-      <c r="F48" s="177"/>
-      <c r="G48" s="178"/>
-      <c r="H48" s="178"/>
-      <c r="I48" s="178"/>
-      <c r="J48" s="179"/>
-      <c r="K48" s="177"/>
-      <c r="L48" s="177"/>
-      <c r="M48" s="177"/>
-      <c r="N48" s="177"/>
-      <c r="O48" s="177"/>
-      <c r="P48" s="177"/>
-      <c r="Q48" s="177"/>
-      <c r="R48" s="177"/>
-      <c r="S48" s="177"/>
+      <c r="A48" s="231">
+        <v>46242</v>
+      </c>
+      <c r="B48" s="232" t="s">
+        <v>260</v>
+      </c>
+      <c r="C48" s="232" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="232" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" s="232">
+        <v>30</v>
+      </c>
+      <c r="F48" s="232">
+        <v>6206</v>
+      </c>
+      <c r="G48" s="233">
+        <v>18438</v>
+      </c>
+      <c r="H48" s="233">
+        <v>18088</v>
+      </c>
+      <c r="I48" s="233">
+        <v>350</v>
+      </c>
+      <c r="J48" s="234">
+        <f t="shared" si="0"/>
+        <v>1.8982536066818528E-2</v>
+      </c>
+      <c r="K48" s="232"/>
+      <c r="L48" s="232"/>
+      <c r="M48" s="232"/>
+      <c r="N48" s="232"/>
+      <c r="O48" s="232"/>
+      <c r="P48" s="232"/>
+      <c r="Q48" s="232"/>
+      <c r="R48" s="232"/>
+      <c r="S48" s="232"/>
     </row>
     <row r="49" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="176"/>
@@ -51686,7 +51857,7 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="37.85546875" customWidth="1"/>
+    <col min="3" max="3" width="38.28515625" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" style="53" customWidth="1"/>
     <col min="6" max="6" width="8.85546875" style="53" customWidth="1"/>
@@ -51713,7 +51884,7 @@
       </c>
       <c r="J1" s="56">
         <f ca="1">TODAY()</f>
-        <v>46242</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="57" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -51905,11 +52076,11 @@
         <v>25</v>
       </c>
       <c r="I7" s="28">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="J7" s="157">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])=0,"-",ROUND((H7+I7)/(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>14349</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -51938,12 +52109,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="28">
-        <v>50</v>
-      </c>
+      <c r="I8" s="28"/>
       <c r="J8" s="157">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])=0,"-",ROUND((H8+I8)/(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>6250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52027,7 +52196,7 @@
       <c r="I12" s="60"/>
       <c r="J12" s="56">
         <f ca="1">TODAY()</f>
-        <v>46242</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -62420,7 +62589,7 @@
         <v>604</v>
       </c>
       <c r="F5" s="237">
-        <v>37128</v>
+        <v>44000</v>
       </c>
       <c r="G5" s="235" t="s">
         <v>602</v>
@@ -62716,7 +62885,7 @@
         <v>610</v>
       </c>
       <c r="F15" s="241">
-        <v>21168</v>
+        <v>26208</v>
       </c>
       <c r="G15" s="239" t="s">
         <v>607</v>
@@ -62746,7 +62915,7 @@
         <v>604</v>
       </c>
       <c r="F16" s="241">
-        <v>6398</v>
+        <v>17000</v>
       </c>
       <c r="G16" s="239" t="s">
         <v>607</v>

--- a/Tubex_Aug26.xlsx
+++ b/Tubex_Aug26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_C911F96073D5E43BF67A80771D70161E2C046278" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_4DD575F5BAD642F1C5B873171F71AC633F53FDCE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4185" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4201" uniqueCount="618">
   <si>
     <t>Slugs Inventory — August 2026 MONTH TO DATE</t>
   </si>
@@ -1821,7 +1821,7 @@
     <t>Top 10 inks = 81.7% of all consumption. Remaining 15 inks share 18.3%.  Source: ERP ST_Stk_Cons_YFI.rpt · May 2025–Apr 2026 · 8,617,293 pcs produced.</t>
   </si>
   <si>
-    <t>FG STOCK IN HAND — Last Updated: 12-Aug-2026</t>
+    <t>FG STOCK IN HAND — Last Updated: 13-Aug-2026</t>
   </si>
   <si>
     <t>Shows latest date only from FG Stock In hand (Production.xlsx). Older dates are discarded. Re-run update_production.py to refresh.</t>
@@ -1869,25 +1869,25 @@
     <t>35</t>
   </si>
   <si>
+    <t>Samsol 45</t>
+  </si>
+  <si>
+    <t>dia 25</t>
+  </si>
+  <si>
+    <t>No Order</t>
+  </si>
+  <si>
     <t>Not Ready</t>
   </si>
   <si>
     <t>Master Carton not Available</t>
   </si>
   <si>
-    <t>Samsol 45</t>
-  </si>
-  <si>
-    <t>dia 25</t>
-  </si>
-  <si>
     <t>Inprogress On Packing</t>
   </si>
   <si>
     <t>Inprogress on Latex</t>
-  </si>
-  <si>
-    <t>Inprogress On Soarting</t>
   </si>
   <si>
     <t>Inprogress on Capping</t>
@@ -3970,8 +3970,8 @@
     <col min="13" max="13" width="14.7109375" style="105" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="105" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="105" customWidth="1"/>
-    <col min="16" max="137" width="8.7109375" style="105" customWidth="1"/>
-    <col min="138" max="16384" width="8.7109375" style="105"/>
+    <col min="16" max="138" width="8.7109375" style="105" customWidth="1"/>
+    <col min="139" max="16384" width="8.7109375" style="105"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -4049,7 +4049,7 @@
       <c r="G3" s="266"/>
       <c r="H3" s="268">
         <f>MAX(Production_Log!$A$3:$A$8963)</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="I3" s="264"/>
       <c r="J3" s="264"/>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="C5" s="195">
         <f>MAX(Production_Log!$A$3:$A$8963)</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D5" s="107" t="s">
         <v>141</v>
@@ -4151,18 +4151,18 @@
       <c r="A6" s="102"/>
       <c r="B6" s="267">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8963=MAX(Production_Log!$A$3:$A$8963))*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v>22134</v>
+        <v>24990</v>
       </c>
       <c r="C6" s="264"/>
       <c r="D6" s="111">
         <f>SUMIF($B$11:$B$66,"TUBE",$H$11:$H$66)</f>
-        <v>174622</v>
+        <v>199612</v>
       </c>
       <c r="E6" s="267"/>
       <c r="F6" s="264"/>
       <c r="G6" s="112">
         <f t="array" ref="G6">IFERROR(SUMPRODUCT((Production_Log!$F$3:$F$8963&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$I$3:$I$8963)/SUMPRODUCT((Production_Log!$F$3:$F$8963&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*(Production_Log!$H$3:$H$8963+Production_Log!$I$3:$I$8963)),"-")</f>
-        <v>2.0694064336668313E-2</v>
+        <v>2.0414973597942799E-2</v>
       </c>
       <c r="H6" s="112"/>
       <c r="I6" s="109"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C7" s="196">
         <f>MAX(Production_Log!$A$3:$A$8963)</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D7" s="114" t="s">
         <v>148</v>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="O7" s="125">
         <f t="shared" ref="O7:O13" si="0">IFERROR(N7/$N$14,"")</f>
-        <v>0.73333333333333328</v>
+        <v>0.7021276595744681</v>
       </c>
       <c r="P7" s="102"/>
       <c r="Q7" s="102"/>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="O8" s="125">
         <f t="shared" si="0"/>
-        <v>0.17777777777777778</v>
+        <v>0.1702127659574468</v>
       </c>
       <c r="P8" s="102"/>
       <c r="Q8" s="102"/>
@@ -4320,11 +4320,11 @@
       </c>
       <c r="N9" s="124">
         <f>IFERROR(INDEX($T$9:$T$22,MATCH(LARGE($U$9:$U$22,3),$U$9:$U$22,0)),"")/60</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" s="125">
         <f t="shared" si="0"/>
-        <v>8.8888888888888892E-2</v>
+        <v>0.1276595744680851</v>
       </c>
       <c r="P9" s="102"/>
       <c r="Q9" s="102"/>
@@ -4334,11 +4334,11 @@
       </c>
       <c r="T9" s="131">
         <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$8963,5)="Press")+(LEFT(Production_Log!$B$3:$B$8963,5)="Print"))*Production_Log!$K$3:$K$8963)</f>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="U9" s="130">
         <f>T9+0.00001</f>
-        <v>120.00001</v>
+        <v>180.00001</v>
       </c>
       <c r="V9" s="104"/>
       <c r="W9" s="104"/>
@@ -4503,15 +4503,15 @@
       </c>
       <c r="H12" s="253">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F12)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v>114478</v>
+        <v>139468</v>
       </c>
       <c r="I12" s="252">
         <f>G12-H12</f>
-        <v>145300</v>
+        <v>120310</v>
       </c>
       <c r="J12" s="254">
         <f>IF(G12=0,"-",H12/G12)</f>
-        <v>0.44067626973800705</v>
+        <v>0.53687379223798781</v>
       </c>
       <c r="K12" s="253">
         <v>128282</v>
@@ -4639,11 +4639,11 @@
       </c>
       <c r="H14" s="259">
         <f>SUM(H11:H13)</f>
-        <v>174622</v>
+        <v>199612</v>
       </c>
       <c r="I14" s="259">
         <f>SUMIF(I11:I13,"&gt;"&amp;0)</f>
-        <v>145300</v>
+        <v>120310</v>
       </c>
       <c r="J14" s="259"/>
       <c r="K14" s="259">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="N14" s="121">
         <f>SUM($T$9:$T$22)/60</f>
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="O14" s="121" t="s">
         <v>174</v>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="H1" s="129">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="I1" s="10"/>
       <c r="J1" s="11"/>
@@ -9150,11 +9150,11 @@
       </c>
       <c r="G3" s="204">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D3,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>114478</v>
+        <v>139468</v>
       </c>
       <c r="H3" s="205">
         <f>F3-G3</f>
-        <v>145300</v>
+        <v>120310</v>
       </c>
       <c r="I3" s="205"/>
     </row>
@@ -9172,11 +9172,11 @@
       </c>
       <c r="G4" s="122">
         <f>SUM(G3:G3)</f>
-        <v>114478</v>
+        <v>139468</v>
       </c>
       <c r="H4" s="122">
         <f>SUMIF(H3:H3, "&gt;0")</f>
-        <v>145300</v>
+        <v>120310</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="11"/>
@@ -9679,19 +9679,19 @@
       </c>
       <c r="E17" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A17)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>1278.6400000000001</v>
+        <v>1058.7280000000001</v>
       </c>
       <c r="F17" s="200">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A17,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A17,TableInventory[Item ID],0)),0)</f>
-        <v>464</v>
+        <v>60</v>
       </c>
       <c r="G17" s="199">
         <f t="shared" si="0"/>
-        <v>-814.6400000000001</v>
+        <v>-998.72800000000007</v>
       </c>
       <c r="H17" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A17)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F17/(SUMPRODUCT((TableBOM[Item ID]=A17)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>58000</v>
+        <v>7500</v>
       </c>
       <c r="I17" s="201" t="str">
         <f t="shared" si="1"/>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="E25" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A25)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>44.752400000000009</v>
+        <v>37.055480000000003</v>
       </c>
       <c r="F25" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A25,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A25,TableInventory[Item ID],0)),0)</f>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G25" s="199">
         <f t="shared" si="0"/>
-        <v>105.24759999999999</v>
+        <v>112.94452</v>
       </c>
       <c r="H25" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A25)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F25/(SUMPRODUCT((TableBOM[Item ID]=A25)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -10222,19 +10222,19 @@
       </c>
       <c r="E29" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A29)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>107.08610000000002</v>
+        <v>88.668470000000013</v>
       </c>
       <c r="F29" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A29,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A29,TableInventory[Item ID],0)),0)</f>
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="G29" s="199">
         <f t="shared" si="0"/>
-        <v>132.91389999999998</v>
+        <v>121.33152999999999</v>
       </c>
       <c r="H29" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A29)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F29/(SUMPRODUCT((TableBOM[Item ID]=A29)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>358209</v>
+        <v>313433</v>
       </c>
       <c r="I29" s="201" t="str">
         <f t="shared" si="2"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="E37" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A37)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>44.752400000000009</v>
+        <v>37.055480000000003</v>
       </c>
       <c r="F37" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A37,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A37,TableInventory[Item ID],0)),0)</f>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="G37" s="199">
         <f t="shared" si="0"/>
-        <v>0.24759999999999138</v>
+        <v>7.9445199999999971</v>
       </c>
       <c r="H37" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A37)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F37/(SUMPRODUCT((TableBOM[Item ID]=A37)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="I37" s="201" t="str">
         <f t="shared" si="2"/>
-        <v>LOW</v>
+        <v>OK</v>
       </c>
       <c r="J37" s="228" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A37)&gt;0)*($H$3&gt;0),$C$3&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A37)&gt;0)*($H$3&gt;0),$C$3&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A37)&gt;0)*($H$3&gt;0),$C$3&amp;", ",""))-2),"")</f>
@@ -11143,19 +11143,19 @@
       </c>
       <c r="E52" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A52)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>148206</v>
+        <v>122716.2</v>
       </c>
       <c r="F52" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A52,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A52,TableInventory[Item ID],0)),0)</f>
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="G52" s="199">
         <f t="shared" si="3"/>
-        <v>-78206</v>
+        <v>-122716.2</v>
       </c>
       <c r="H52" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A52)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F52/(SUMPRODUCT((TableBOM[Item ID]=A52)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="I52" s="201" t="str">
         <f t="shared" si="4"/>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="E65" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A65)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>671.54172800000003</v>
+        <v>556.04394560000003</v>
       </c>
       <c r="F65" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A65,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A65,TableInventory[Item ID],0)),0)</f>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="G65" s="199">
         <f t="shared" si="3"/>
-        <v>-478.54172800000003</v>
+        <v>-363.04394560000003</v>
       </c>
       <c r="H65" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A65)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F65/(SUMPRODUCT((TableBOM[Item ID]=A65)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="E69" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A69)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>1.3297856000000001</v>
+        <v>1.1010771200000002</v>
       </c>
       <c r="F69" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A69,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A69,TableInventory[Item ID],0)),0)</f>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="G69" s="199">
         <f t="shared" si="3"/>
-        <v>38.670214399999999</v>
+        <v>38.898922880000001</v>
       </c>
       <c r="H69" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A69)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F69/(SUMPRODUCT((TableBOM[Item ID]=A69)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="E71" s="199">
         <f>SUMPRODUCT((TableBOM[Item ID]=A71)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$3,TableBOM[Product ID],$H$3:$H$3)/1000)</f>
-        <v>24.933479999999999</v>
+        <v>20.645195999999999</v>
       </c>
       <c r="F71" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A71,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A71,TableInventory[Item ID],0)),0)</f>
@@ -11879,7 +11879,7 @@
       </c>
       <c r="G71" s="199">
         <f t="shared" ref="G71:G102" si="6">F71-E71</f>
-        <v>402.06652000000003</v>
+        <v>406.354804</v>
       </c>
       <c r="H71" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A71)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F71/(SUMPRODUCT((TableBOM[Item ID]=A71)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -11913,11 +11913,11 @@
       </c>
       <c r="F72" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A72,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A72,TableInventory[Item ID],0)),0)</f>
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="G72" s="199">
         <f t="shared" si="6"/>
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="H72" s="226" t="str">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A72)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F72/(SUMPRODUCT((TableBOM[Item ID]=A72)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -15618,109 +15618,218 @@
       <c r="S58" s="232"/>
     </row>
     <row r="59" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="176"/>
-      <c r="B59" s="177"/>
-      <c r="C59" s="177"/>
-      <c r="D59" s="177"/>
-      <c r="E59" s="177"/>
-      <c r="F59" s="177"/>
-      <c r="G59" s="178"/>
-      <c r="H59" s="178"/>
-      <c r="I59" s="178"/>
-      <c r="J59" s="179"/>
-      <c r="K59" s="177"/>
-      <c r="L59" s="177"/>
-      <c r="M59" s="177"/>
-      <c r="N59" s="177"/>
-      <c r="O59" s="177"/>
-      <c r="P59" s="177"/>
-      <c r="Q59" s="177"/>
-      <c r="R59" s="177"/>
-      <c r="S59" s="177"/>
+      <c r="A59" s="231">
+        <v>46246</v>
+      </c>
+      <c r="B59" s="232" t="s">
+        <v>316</v>
+      </c>
+      <c r="C59" s="232" t="s">
+        <v>167</v>
+      </c>
+      <c r="D59" s="232" t="s">
+        <v>168</v>
+      </c>
+      <c r="E59" s="232">
+        <v>30</v>
+      </c>
+      <c r="F59" s="232">
+        <v>6206</v>
+      </c>
+      <c r="G59" s="233">
+        <v>24000</v>
+      </c>
+      <c r="H59" s="233">
+        <v>23605</v>
+      </c>
+      <c r="I59" s="233">
+        <v>395</v>
+      </c>
+      <c r="J59" s="234">
+        <f t="shared" si="1"/>
+        <v>1.6458333333333332E-2</v>
+      </c>
+      <c r="K59" s="232"/>
+      <c r="L59" s="232"/>
+      <c r="M59" s="232"/>
+      <c r="N59" s="232"/>
+      <c r="O59" s="232"/>
+      <c r="P59" s="232"/>
+      <c r="Q59" s="232"/>
+      <c r="R59" s="232"/>
+      <c r="S59" s="232"/>
     </row>
     <row r="60" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="176"/>
-      <c r="B60" s="177"/>
-      <c r="C60" s="177"/>
-      <c r="D60" s="177"/>
-      <c r="E60" s="177"/>
-      <c r="F60" s="177"/>
-      <c r="G60" s="178"/>
-      <c r="H60" s="178"/>
-      <c r="I60" s="178"/>
-      <c r="J60" s="179"/>
-      <c r="K60" s="177"/>
-      <c r="L60" s="177"/>
-      <c r="M60" s="177"/>
-      <c r="N60" s="177"/>
-      <c r="O60" s="177"/>
-      <c r="P60" s="177"/>
-      <c r="Q60" s="177"/>
-      <c r="R60" s="177"/>
-      <c r="S60" s="177"/>
+      <c r="A60" s="231">
+        <v>46246</v>
+      </c>
+      <c r="B60" s="232" t="s">
+        <v>317</v>
+      </c>
+      <c r="C60" s="232" t="s">
+        <v>167</v>
+      </c>
+      <c r="D60" s="232" t="s">
+        <v>168</v>
+      </c>
+      <c r="E60" s="232">
+        <v>30</v>
+      </c>
+      <c r="F60" s="232">
+        <v>6206</v>
+      </c>
+      <c r="G60" s="233">
+        <v>27370</v>
+      </c>
+      <c r="H60" s="233">
+        <v>27350</v>
+      </c>
+      <c r="I60" s="233">
+        <v>20</v>
+      </c>
+      <c r="J60" s="234">
+        <f t="shared" si="1"/>
+        <v>7.3072707343807086E-4</v>
+      </c>
+      <c r="K60" s="232"/>
+      <c r="L60" s="232"/>
+      <c r="M60" s="232"/>
+      <c r="N60" s="232"/>
+      <c r="O60" s="232"/>
+      <c r="P60" s="232"/>
+      <c r="Q60" s="232"/>
+      <c r="R60" s="232"/>
+      <c r="S60" s="232"/>
     </row>
     <row r="61" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="176"/>
-      <c r="B61" s="177"/>
-      <c r="C61" s="177"/>
-      <c r="D61" s="177"/>
-      <c r="E61" s="177"/>
-      <c r="F61" s="177"/>
-      <c r="G61" s="178"/>
-      <c r="H61" s="178"/>
-      <c r="I61" s="178"/>
-      <c r="J61" s="179"/>
-      <c r="K61" s="177"/>
-      <c r="L61" s="177"/>
-      <c r="M61" s="177"/>
-      <c r="N61" s="177"/>
-      <c r="O61" s="177"/>
-      <c r="P61" s="177"/>
-      <c r="Q61" s="177"/>
-      <c r="R61" s="177"/>
-      <c r="S61" s="177"/>
+      <c r="A61" s="231">
+        <v>46246</v>
+      </c>
+      <c r="B61" s="232" t="s">
+        <v>318</v>
+      </c>
+      <c r="C61" s="232" t="s">
+        <v>181</v>
+      </c>
+      <c r="D61" s="232" t="s">
+        <v>182</v>
+      </c>
+      <c r="E61" s="232" t="s">
+        <v>183</v>
+      </c>
+      <c r="F61" s="232">
+        <v>8001</v>
+      </c>
+      <c r="G61" s="233">
+        <v>0</v>
+      </c>
+      <c r="H61" s="233">
+        <v>0</v>
+      </c>
+      <c r="I61" s="233">
+        <v>0</v>
+      </c>
+      <c r="J61" s="234" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K61" s="232"/>
+      <c r="L61" s="232">
+        <v>960</v>
+      </c>
+      <c r="M61" s="232"/>
+      <c r="N61" s="232"/>
+      <c r="O61" s="232"/>
+      <c r="P61" s="232"/>
+      <c r="Q61" s="232"/>
+      <c r="R61" s="232"/>
+      <c r="S61" s="232"/>
     </row>
     <row r="62" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="176"/>
-      <c r="B62" s="177"/>
-      <c r="C62" s="177"/>
-      <c r="D62" s="177"/>
-      <c r="E62" s="177"/>
-      <c r="F62" s="177"/>
-      <c r="G62" s="178"/>
-      <c r="H62" s="178"/>
-      <c r="I62" s="178"/>
-      <c r="J62" s="179"/>
-      <c r="K62" s="177"/>
-      <c r="L62" s="177"/>
-      <c r="M62" s="177"/>
-      <c r="N62" s="177"/>
-      <c r="O62" s="177"/>
-      <c r="P62" s="177"/>
-      <c r="Q62" s="177"/>
-      <c r="R62" s="177"/>
-      <c r="S62" s="177"/>
+      <c r="A62" s="231">
+        <v>46246</v>
+      </c>
+      <c r="B62" s="232" t="s">
+        <v>319</v>
+      </c>
+      <c r="C62" s="232" t="s">
+        <v>167</v>
+      </c>
+      <c r="D62" s="232" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" s="232">
+        <v>30</v>
+      </c>
+      <c r="F62" s="232">
+        <v>6206</v>
+      </c>
+      <c r="G62" s="233">
+        <v>17600</v>
+      </c>
+      <c r="H62" s="233">
+        <v>17485</v>
+      </c>
+      <c r="I62" s="233">
+        <v>115</v>
+      </c>
+      <c r="J62" s="234">
+        <f t="shared" si="1"/>
+        <v>6.5340909090909087E-3</v>
+      </c>
+      <c r="K62" s="232">
+        <v>60</v>
+      </c>
+      <c r="L62" s="232"/>
+      <c r="M62" s="232"/>
+      <c r="N62" s="232"/>
+      <c r="O62" s="232"/>
+      <c r="P62" s="232"/>
+      <c r="Q62" s="232"/>
+      <c r="R62" s="232"/>
+      <c r="S62" s="232"/>
     </row>
     <row r="63" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="176"/>
-      <c r="B63" s="177"/>
-      <c r="C63" s="177"/>
-      <c r="D63" s="177"/>
-      <c r="E63" s="177"/>
-      <c r="F63" s="177"/>
-      <c r="G63" s="178"/>
-      <c r="H63" s="178"/>
-      <c r="I63" s="178"/>
-      <c r="J63" s="179"/>
-      <c r="K63" s="177"/>
-      <c r="L63" s="177"/>
-      <c r="M63" s="177"/>
-      <c r="N63" s="177"/>
-      <c r="O63" s="177"/>
-      <c r="P63" s="177"/>
-      <c r="Q63" s="177"/>
-      <c r="R63" s="177"/>
-      <c r="S63" s="177"/>
+      <c r="A63" s="231">
+        <v>46246</v>
+      </c>
+      <c r="B63" s="232" t="s">
+        <v>320</v>
+      </c>
+      <c r="C63" s="232" t="s">
+        <v>167</v>
+      </c>
+      <c r="D63" s="232" t="s">
+        <v>168</v>
+      </c>
+      <c r="E63" s="232">
+        <v>30</v>
+      </c>
+      <c r="F63" s="232">
+        <v>6206</v>
+      </c>
+      <c r="G63" s="233">
+        <v>25460</v>
+      </c>
+      <c r="H63" s="233">
+        <v>24990</v>
+      </c>
+      <c r="I63" s="233">
+        <v>470</v>
+      </c>
+      <c r="J63" s="234">
+        <f t="shared" si="1"/>
+        <v>1.8460329929300863E-2</v>
+      </c>
+      <c r="K63" s="232"/>
+      <c r="L63" s="232"/>
+      <c r="M63" s="232"/>
+      <c r="N63" s="232"/>
+      <c r="O63" s="232"/>
+      <c r="P63" s="232"/>
+      <c r="Q63" s="232"/>
+      <c r="R63" s="232"/>
+      <c r="S63" s="232"/>
     </row>
     <row r="64" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="176"/>
@@ -52101,7 +52210,7 @@
       </c>
       <c r="J1" s="56">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="57" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -52318,18 +52427,18 @@
         <v>1089</v>
       </c>
       <c r="G8" s="28">
-        <v>761</v>
+        <v>1200</v>
       </c>
       <c r="H8" s="29">
         <f t="shared" si="0"/>
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="I8" s="28">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="J8" s="157">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])=0,"-",ROUND((H8+I8)/(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>58000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52352,13 +52461,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="28">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H9" s="29">
         <f t="shared" si="0"/>
-        <v>444</v>
-      </c>
-      <c r="I9" s="28"/>
+        <v>425</v>
+      </c>
+      <c r="I9" s="28">
+        <v>19</v>
+      </c>
       <c r="J9" s="157">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A9,TableBOM[Per 1000 Units])=0,"-",ROUND((H9+I9)/(AVERAGEIF(TableBOM[Item ID],A9,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
         <v>40872</v>
@@ -52413,7 +52524,7 @@
       <c r="I12" s="60"/>
       <c r="J12" s="56">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -52739,16 +52850,16 @@
         <v>210</v>
       </c>
       <c r="G22" s="144">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H22" s="145">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="I22" s="144"/>
       <c r="J22" s="161">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A22,TableBOM[Per 1000 Units])=0,"-",ROUND((H22+I22)/(AVERAGEIF(TableBOM[Item ID],A22,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>442305</v>
+        <v>387017</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53617,16 +53728,16 @@
         <v>0</v>
       </c>
       <c r="G46" s="144">
-        <v>123000</v>
+        <v>193000</v>
       </c>
       <c r="H46" s="145">
         <f t="shared" ref="H46:H77" si="2">E46+F46-G46</f>
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="I46" s="144"/>
       <c r="J46" s="161">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A46,TableBOM[Per 1000 Units])=0,"-",ROUND((H46+I46)/(AVERAGEIF(TableBOM[Item ID],A46,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="K46" s="166"/>
       <c r="L46" s="146"/>
@@ -54235,16 +54346,16 @@
         <v>100</v>
       </c>
       <c r="G62" s="144">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H62" s="145">
         <f t="shared" si="2"/>
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="I62" s="144"/>
       <c r="J62" s="161">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A62,TableBOM[Per 1000 Units])=0,"-",ROUND((H62+I62)/(AVERAGEIF(TableBOM[Item ID],A62,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>4166667</v>
+        <v>3750000</v>
       </c>
       <c r="K62" s="167"/>
       <c r="L62" s="147"/>
@@ -54925,11 +55036,11 @@
         <v>2</v>
       </c>
       <c r="G80" s="154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H80" s="155">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" s="154"/>
       <c r="J80" s="160" t="str">
@@ -62679,14 +62790,14 @@
   </autoFilter>
   <mergeCells count="9">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A92:K92"/>
-    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A65:K65"/>
     <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A75:K75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -62970,27 +63081,27 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="239">
+      <c r="A11" s="235">
         <v>8</v>
       </c>
-      <c r="B11" s="239"/>
-      <c r="C11" s="240" t="s">
-        <v>599</v>
-      </c>
-      <c r="D11" s="240" t="s">
-        <v>600</v>
-      </c>
-      <c r="E11" s="239" t="s">
-        <v>601</v>
-      </c>
-      <c r="F11" s="241">
-        <v>4600</v>
-      </c>
-      <c r="G11" s="239" t="s">
+      <c r="B11" s="235"/>
+      <c r="C11" s="236" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="236" t="s">
         <v>607</v>
       </c>
-      <c r="H11" s="242" t="s">
+      <c r="E11" s="235" t="s">
         <v>608</v>
+      </c>
+      <c r="F11" s="237">
+        <v>23520</v>
+      </c>
+      <c r="G11" s="235" t="s">
+        <v>602</v>
+      </c>
+      <c r="H11" s="238" t="s">
+        <v>609</v>
       </c>
       <c r="I11" s="72">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B11)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
@@ -63001,26 +63112,24 @@
       <c r="A12" s="239">
         <v>9</v>
       </c>
-      <c r="B12" s="239">
-        <v>8001</v>
-      </c>
+      <c r="B12" s="239"/>
       <c r="C12" s="240" t="s">
-        <v>181</v>
+        <v>599</v>
       </c>
       <c r="D12" s="240" t="s">
-        <v>182</v>
+        <v>600</v>
       </c>
       <c r="E12" s="239" t="s">
         <v>601</v>
       </c>
       <c r="F12" s="241">
-        <v>18400</v>
+        <v>4600</v>
       </c>
       <c r="G12" s="239" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H12" s="242" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="I12" s="72">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B12)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
@@ -63031,21 +63140,23 @@
       <c r="A13" s="239">
         <v>10</v>
       </c>
-      <c r="B13" s="239"/>
+      <c r="B13" s="239">
+        <v>8001</v>
+      </c>
       <c r="C13" s="240" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="D13" s="240" t="s">
-        <v>609</v>
+        <v>182</v>
       </c>
       <c r="E13" s="239" t="s">
+        <v>601</v>
+      </c>
+      <c r="F13" s="241">
+        <v>18400</v>
+      </c>
+      <c r="G13" s="239" t="s">
         <v>610</v>
-      </c>
-      <c r="F13" s="241">
-        <v>43008</v>
-      </c>
-      <c r="G13" s="239" t="s">
-        <v>607</v>
       </c>
       <c r="H13" s="242" t="s">
         <v>611</v>
@@ -63059,30 +63170,28 @@
       <c r="A14" s="239">
         <v>11</v>
       </c>
-      <c r="B14" s="239">
-        <v>6206</v>
-      </c>
+      <c r="B14" s="239"/>
       <c r="C14" s="240" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D14" s="240" t="s">
-        <v>168</v>
+        <v>607</v>
       </c>
       <c r="E14" s="239" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="F14" s="241">
-        <v>11000</v>
+        <v>43008</v>
       </c>
       <c r="G14" s="239" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H14" s="242" t="s">
         <v>612</v>
       </c>
       <c r="I14" s="73">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B14)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63105,10 +63214,10 @@
         <v>11000</v>
       </c>
       <c r="G15" s="239" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H15" s="242" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="I15" s="73">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B15)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
@@ -63119,28 +63228,30 @@
       <c r="A16" s="239">
         <v>13</v>
       </c>
-      <c r="B16" s="239"/>
+      <c r="B16" s="239">
+        <v>6206</v>
+      </c>
       <c r="C16" s="240" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D16" s="240" t="s">
-        <v>609</v>
+        <v>168</v>
       </c>
       <c r="E16" s="239" t="s">
+        <v>604</v>
+      </c>
+      <c r="F16" s="241">
+        <v>35990</v>
+      </c>
+      <c r="G16" s="239" t="s">
         <v>610</v>
       </c>
-      <c r="F16" s="241">
-        <v>23520</v>
-      </c>
-      <c r="G16" s="239" t="s">
-        <v>607</v>
-      </c>
       <c r="H16" s="242" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="I16" s="73">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B16)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63163,7 +63274,7 @@
         <v>11340</v>
       </c>
       <c r="G17" s="239" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H17" s="242" t="s">
         <v>614</v>
@@ -63253,7 +63364,7 @@
         <v>15876</v>
       </c>
       <c r="G20" s="239" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H20" s="242" t="s">
         <v>616</v>
@@ -63283,7 +63394,7 @@
         <v>33660</v>
       </c>
       <c r="G21" s="239" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H21" s="242" t="s">
         <v>616</v>

--- a/Tubex_Aug26.xlsx
+++ b/Tubex_Aug26.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_601DF1DA98759B46B83E03B9E04FAE33B3906977" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D346C11B-C7AC-40BE-865B-0EFEE6D789E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,8 +44,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4230" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4234" uniqueCount="620">
   <si>
     <t>TUBEX  — August 2026 Month to Date Report</t>
   </si>
@@ -1904,6 +1926,9 @@
   <si>
     <t>19</t>
   </si>
+  <si>
+    <t>Caps &amp; Slug Shortage</t>
+  </si>
 </sst>
 </file>
 
@@ -3520,12 +3545,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="31" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="31" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3535,19 +3573,6 @@
     <xf numFmtId="0" fontId="37" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="31" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3961,7 +3986,7 @@
     <col min="1" max="1" width="1.5703125" style="105" customWidth="1"/>
     <col min="2" max="2" width="7" style="105" customWidth="1"/>
     <col min="3" max="3" width="32.7109375" style="105" customWidth="1"/>
-    <col min="4" max="4" width="38.7109375" style="105" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" style="105" customWidth="1"/>
     <col min="5" max="5" width="8.85546875" style="103" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="105" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" style="106" customWidth="1"/>
@@ -4009,22 +4034,22 @@
     </row>
     <row r="2" spans="1:29" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="102"/>
-      <c r="B2" s="269" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="262"/>
-      <c r="D2" s="262"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="262"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="262"/>
-      <c r="I2" s="262"/>
-      <c r="J2" s="262"/>
-      <c r="K2" s="262"/>
-      <c r="L2" s="262"/>
-      <c r="M2" s="262"/>
-      <c r="N2" s="262"/>
-      <c r="O2" s="262"/>
+      <c r="B2" s="263" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="264"/>
+      <c r="D2" s="264"/>
+      <c r="E2" s="265"/>
+      <c r="F2" s="264"/>
+      <c r="G2" s="266"/>
+      <c r="H2" s="264"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="264"/>
+      <c r="K2" s="264"/>
+      <c r="L2" s="264"/>
+      <c r="M2" s="264"/>
+      <c r="N2" s="264"/>
+      <c r="O2" s="264"/>
       <c r="P2" s="102"/>
       <c r="Q2" s="102"/>
       <c r="R2" s="102"/>
@@ -4042,25 +4067,25 @@
     </row>
     <row r="3" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="102"/>
-      <c r="B3" s="261" t="s">
+      <c r="B3" s="269" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="262"/>
-      <c r="D3" s="262"/>
-      <c r="E3" s="263"/>
-      <c r="F3" s="262"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="266">
+      <c r="C3" s="264"/>
+      <c r="D3" s="264"/>
+      <c r="E3" s="265"/>
+      <c r="F3" s="264"/>
+      <c r="G3" s="266"/>
+      <c r="H3" s="271">
         <f>MAX(Production_Log!$A$3:$A$8961)</f>
-        <v>46248</v>
-      </c>
-      <c r="I3" s="262"/>
-      <c r="J3" s="262"/>
-      <c r="K3" s="262"/>
-      <c r="L3" s="262"/>
-      <c r="M3" s="262"/>
-      <c r="N3" s="262"/>
-      <c r="O3" s="262"/>
+        <v>46250</v>
+      </c>
+      <c r="I3" s="264"/>
+      <c r="J3" s="264"/>
+      <c r="K3" s="264"/>
+      <c r="L3" s="264"/>
+      <c r="M3" s="264"/>
+      <c r="N3" s="264"/>
+      <c r="O3" s="264"/>
       <c r="P3" s="102"/>
       <c r="Q3" s="102"/>
       <c r="R3" s="102"/>
@@ -4113,22 +4138,22 @@
       </c>
       <c r="C5" s="195">
         <f>MAX(Production_Log!$A$3:$A$8961)</f>
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="D5" s="107" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="107"/>
       <c r="F5" s="108"/>
-      <c r="G5" s="268" t="s">
+      <c r="G5" s="267" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="262"/>
+      <c r="H5" s="264"/>
       <c r="I5" s="109"/>
-      <c r="J5" s="268" t="s">
+      <c r="J5" s="267" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="262"/>
+      <c r="K5" s="264"/>
       <c r="L5" s="136"/>
       <c r="M5" s="110" t="s">
         <v>6</v>
@@ -4152,28 +4177,28 @@
     </row>
     <row r="6" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="102"/>
-      <c r="B6" s="265">
+      <c r="B6" s="270">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8961=MAX(Production_Log!$A$3:$A$8961))*(LEFT(Production_Log!$B$3:$B$8961,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8961)))*Production_Log!$H$3:$H$8961)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="262"/>
+      <c r="C6" s="264"/>
       <c r="D6" s="111">
         <f>SUMIF($B$11:$B$66,"TUBE",$H$11:$H$66)</f>
         <v>212464</v>
       </c>
-      <c r="E6" s="265"/>
-      <c r="F6" s="262"/>
+      <c r="E6" s="270"/>
+      <c r="F6" s="264"/>
       <c r="G6" s="112">
         <f t="array" ref="G6">IFERROR(SUMPRODUCT((Production_Log!$F$3:$F$8961&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8961,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8961)))*Production_Log!$I$3:$I$8961)/SUMPRODUCT((Production_Log!$F$3:$F$8961&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8961,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8961)))*(Production_Log!$H$3:$H$8961+Production_Log!$I$3:$I$8961)),"-")</f>
         <v>2.0605345404593103E-2</v>
       </c>
       <c r="H6" s="112"/>
       <c r="I6" s="109"/>
-      <c r="J6" s="265">
+      <c r="J6" s="270">
         <f>SUMIF($B$11:$B$66,"TUBE",$K$11:$K$66)</f>
         <v>164682</v>
       </c>
-      <c r="K6" s="262"/>
+      <c r="K6" s="264"/>
       <c r="L6" s="113"/>
       <c r="M6" s="137" t="s">
         <v>7</v>
@@ -4206,17 +4231,17 @@
       </c>
       <c r="C7" s="196">
         <f>MAX(Production_Log!$A$3:$A$8961)</f>
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="D7" s="114" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="114"/>
       <c r="F7" s="115"/>
-      <c r="G7" s="267" t="s">
+      <c r="G7" s="272" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="262"/>
+      <c r="H7" s="264"/>
       <c r="I7" s="116"/>
       <c r="J7" s="115" t="s">
         <v>5</v>
@@ -4252,28 +4277,28 @@
     </row>
     <row r="8" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="102"/>
-      <c r="B8" s="270">
+      <c r="B8" s="268">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8961=MAX(Production_Log!$A$3:$A$8961))*(Production_Log!$B$3:$B$8961="PF Machine")*Production_Log!$H$3:$H$8961)</f>
-        <v>8740</v>
-      </c>
-      <c r="C8" s="262"/>
+        <v>0</v>
+      </c>
+      <c r="C8" s="264"/>
       <c r="D8" s="117">
         <f>SUMIF($B$11:$B$66,"PET",$H$11:$H$66)</f>
         <v>60375</v>
       </c>
-      <c r="E8" s="270"/>
-      <c r="F8" s="262"/>
+      <c r="E8" s="268"/>
+      <c r="F8" s="264"/>
       <c r="G8" s="118">
         <f t="array" ref="G8">IFERROR(SUMPRODUCT((Production_Log!$B$3:$B$8961="PF Machine")*Production_Log!$I$3:$I$8961)/SUMPRODUCT((Production_Log!$B$3:$B$8961="PF Machine")*(Production_Log!$H$3:$H$8961+Production_Log!$I$3:$I$8961)),0)</f>
         <v>5.0483604623732012E-2</v>
       </c>
       <c r="H8" s="118"/>
       <c r="I8" s="116"/>
-      <c r="J8" s="270">
+      <c r="J8" s="268">
         <f>SUMIF($B$11:$B$66,"PET",$K$11:$K$66)</f>
         <v>31280</v>
       </c>
-      <c r="K8" s="262"/>
+      <c r="K8" s="264"/>
       <c r="L8" s="119"/>
       <c r="M8" s="123" t="str">
         <f>IFERROR(INDEX($S$9:$S$22,MATCH(LARGE($U$9:$U$22,2),$U$9:$U$22,0)),"")</f>
@@ -4304,19 +4329,19 @@
     </row>
     <row r="9" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="102"/>
-      <c r="B9" s="271" t="s">
+      <c r="B9" s="261" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="272"/>
-      <c r="D9" s="272"/>
-      <c r="E9" s="272"/>
-      <c r="F9" s="272"/>
-      <c r="G9" s="272"/>
-      <c r="H9" s="272"/>
-      <c r="I9" s="272"/>
-      <c r="J9" s="272"/>
-      <c r="K9" s="272"/>
-      <c r="L9" s="272"/>
+      <c r="C9" s="262"/>
+      <c r="D9" s="262"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="262"/>
+      <c r="G9" s="262"/>
+      <c r="H9" s="262"/>
+      <c r="I9" s="262"/>
+      <c r="J9" s="262"/>
+      <c r="K9" s="262"/>
+      <c r="L9" s="262"/>
       <c r="M9" s="123" t="str">
         <f>IFERROR(INDEX($S$9:$S$22,MATCH(LARGE($U$9:$U$22,3),$U$9:$U$22,0)),"")</f>
         <v>Mechanical</v>
@@ -4790,17 +4815,17 @@
       <c r="G17" s="252">
         <v>701257</v>
       </c>
-      <c r="H17" s="253">
-        <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F17)*Production_Log!$H$3:$H$8963)</f>
-        <v>60375</v>
+      <c r="H17" s="253" cm="1">
+        <f t="array" ref="H17">SUMPRODUCT((Production_Log!$F$3:$F$8963=F17)*Production_Log!$H$3:$H$8963)-13960</f>
+        <v>46415</v>
       </c>
       <c r="I17" s="252">
         <f>G17-H17</f>
-        <v>640882</v>
+        <v>654842</v>
       </c>
       <c r="J17" s="254">
         <f>IF(G17=0,"-",H17/G17)</f>
-        <v>8.6095397265196646E-2</v>
+        <v>6.6188287603546198E-2</v>
       </c>
       <c r="K17" s="253">
         <v>31280</v>
@@ -4855,16 +4880,15 @@
         <v>13960</v>
       </c>
       <c r="H18" s="253">
-        <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F18)*Production_Log!$H$3:$H$8963)</f>
-        <v>0</v>
+        <v>13960</v>
       </c>
       <c r="I18" s="252">
         <f>G18-H18</f>
-        <v>13960</v>
+        <v>0</v>
       </c>
       <c r="J18" s="254">
         <f>IF(G18=0,"-",H18/G18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="253"/>
       <c r="L18" s="255" t="s">
@@ -9062,8 +9086,8 @@
     <col min="6" max="6" width="16.5703125" style="4" customWidth="1"/>
     <col min="7" max="7" width="11.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="17.5703125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="15" style="3" customWidth="1"/>
-    <col min="10" max="10" width="46.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="45.42578125" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
@@ -9083,7 +9107,7 @@
       </c>
       <c r="H1" s="129">
         <f ca="1">TODAY()</f>
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="I1" s="10"/>
       <c r="J1" s="11"/>
@@ -9163,7 +9187,9 @@
         <f>F3-G3</f>
         <v>107458</v>
       </c>
-      <c r="I3" s="205"/>
+      <c r="I3" s="205" t="s">
+        <v>619</v>
+      </c>
     </row>
     <row r="4" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
@@ -9690,15 +9716,15 @@
       </c>
       <c r="F17" s="200">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A17,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A17,TableInventory[Item ID],0)),0)</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G17" s="199">
         <f t="shared" si="0"/>
-        <v>-885.63040000000001</v>
+        <v>-945.63040000000001</v>
       </c>
       <c r="H17" s="226">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A17)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F17/(SUMPRODUCT((TableBOM[Item ID]=A17)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="I17" s="201" t="str">
         <f t="shared" si="1"/>
@@ -9782,11 +9808,11 @@
       </c>
       <c r="F19" s="199">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A19,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A19,TableInventory[Item ID],0)),0)</f>
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="G19" s="199">
         <f t="shared" si="0"/>
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="H19" s="226" t="str">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A19)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])=0,"-",ROUND(F19/(SUMPRODUCT((TableBOM[Item ID]=A19)*(TableBOM[Product ID]=$D$3)*($H$3&gt;0)*TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -11885,7 +11911,7 @@
         <v>427</v>
       </c>
       <c r="G71" s="199">
-        <f t="shared" ref="G71:G102" si="6">F71-E71</f>
+        <f t="shared" ref="G71:G88" si="6">F71-E71</f>
         <v>408.56020719999998</v>
       </c>
       <c r="H71" s="226">
@@ -12702,11 +12728,11 @@
       </c>
       <c r="G95" s="220">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D95,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>60375</v>
+        <v>46415</v>
       </c>
       <c r="H95" s="221">
         <f>F95-G95</f>
-        <v>640882</v>
+        <v>654842</v>
       </c>
       <c r="I95" s="192"/>
     </row>
@@ -12731,11 +12757,11 @@
       </c>
       <c r="G96" s="222">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D96,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>0</v>
+        <v>13960</v>
       </c>
       <c r="H96" s="223">
         <f>F96-G96</f>
-        <v>13960</v>
+        <v>0</v>
       </c>
       <c r="I96" s="192"/>
       <c r="J96" s="189"/>
@@ -15997,7 +16023,7 @@
         <v>50</v>
       </c>
       <c r="J67" s="234">
-        <f t="shared" ref="J67:J98" si="2">IFERROR(I67/(H67+I67),"")</f>
+        <f t="shared" ref="J67:J73" si="2">IFERROR(I67/(H67+I67),"")</f>
         <v>7.1942446043165471E-3</v>
       </c>
       <c r="K67" s="232"/>
@@ -16269,25 +16295,46 @@
       <c r="S73" s="232"/>
     </row>
     <row r="74" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="176"/>
-      <c r="B74" s="177"/>
-      <c r="C74" s="177"/>
-      <c r="D74" s="177"/>
-      <c r="E74" s="177"/>
-      <c r="F74" s="177"/>
-      <c r="G74" s="178"/>
-      <c r="H74" s="178"/>
-      <c r="I74" s="178"/>
-      <c r="J74" s="179"/>
-      <c r="K74" s="177"/>
-      <c r="L74" s="177"/>
-      <c r="M74" s="177"/>
-      <c r="N74" s="177"/>
-      <c r="O74" s="177"/>
-      <c r="P74" s="177"/>
-      <c r="Q74" s="177"/>
-      <c r="R74" s="177"/>
-      <c r="S74" s="177"/>
+      <c r="A74" s="231">
+        <v>46250</v>
+      </c>
+      <c r="B74" s="232" t="s">
+        <v>262</v>
+      </c>
+      <c r="C74" s="232" t="s">
+        <v>30</v>
+      </c>
+      <c r="D74" s="232" t="s">
+        <v>31</v>
+      </c>
+      <c r="E74" s="232">
+        <v>30</v>
+      </c>
+      <c r="F74" s="232">
+        <v>6206</v>
+      </c>
+      <c r="G74" s="233">
+        <v>0</v>
+      </c>
+      <c r="H74" s="233">
+        <v>0</v>
+      </c>
+      <c r="I74" s="233">
+        <v>0</v>
+      </c>
+      <c r="J74" s="234" t="str">
+        <f t="shared" ref="J74" si="3">IFERROR(I74/(H74+I74),"")</f>
+        <v/>
+      </c>
+      <c r="K74" s="232"/>
+      <c r="L74" s="232"/>
+      <c r="M74" s="232"/>
+      <c r="N74" s="232"/>
+      <c r="O74" s="232"/>
+      <c r="P74" s="232"/>
+      <c r="Q74" s="232"/>
+      <c r="R74" s="232"/>
+      <c r="S74" s="232"/>
     </row>
     <row r="75" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="176"/>
@@ -52383,19 +52430,19 @@
       <c r="A1" s="278" t="s">
         <v>333</v>
       </c>
-      <c r="B1" s="272"/>
-      <c r="C1" s="272"/>
-      <c r="D1" s="272"/>
-      <c r="E1" s="272"/>
-      <c r="F1" s="272"/>
-      <c r="G1" s="272"/>
-      <c r="H1" s="272"/>
+      <c r="B1" s="262"/>
+      <c r="C1" s="262"/>
+      <c r="D1" s="262"/>
+      <c r="E1" s="262"/>
+      <c r="F1" s="262"/>
+      <c r="G1" s="262"/>
+      <c r="H1" s="262"/>
       <c r="I1" s="55" t="s">
         <v>114</v>
       </c>
       <c r="J1" s="56">
         <f ca="1">TODAY()</f>
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="57" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -52618,12 +52665,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="28">
-        <v>60</v>
-      </c>
+      <c r="I8" s="28"/>
       <c r="J8" s="157">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])=0,"-",ROUND((H8+I8)/(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>7500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52652,12 +52697,10 @@
         <f t="shared" si="0"/>
         <v>425</v>
       </c>
-      <c r="I9" s="28">
-        <v>19</v>
-      </c>
+      <c r="I9" s="28"/>
       <c r="J9" s="157">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A9,TableBOM[Per 1000 Units])=0,"-",ROUND((H9+I9)/(AVERAGEIF(TableBOM[Item ID],A9,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>40872</v>
+        <v>39123</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52709,7 +52752,7 @@
       <c r="I12" s="60"/>
       <c r="J12" s="56">
         <f ca="1">TODAY()</f>
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -55154,7 +55197,7 @@
         <v>0</v>
       </c>
       <c r="H78" s="145">
-        <f t="shared" ref="H78:H109" si="3">E78+F78-G78</f>
+        <f t="shared" ref="H78:H92" si="3">E78+F78-G78</f>
         <v>1</v>
       </c>
       <c r="I78" s="144"/>
@@ -62974,15 +63017,15 @@
     </sortState>
   </autoFilter>
   <mergeCells count="9">
+    <mergeCell ref="A92:K92"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A23:K23"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A92:K92"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A81:K81"/>
-    <mergeCell ref="A75:K75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
